--- a/experiment/HAT+CNN_bestx4/Test/results_table_HAT+CNN.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results_table_HAT+CNN.xlsx
@@ -570,31 +570,31 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.208/
+          <t>32.211/
 0.8937</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.641/
+          <t>28.639/
 0.7824</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.585/
-0.7373</t>
+          <t>27.583/
+0.7372</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>25.986/
-0.7834</t>
+          <t>25.978/
+0.7833</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.469/
+          <t>30.478/
 0.9089</t>
         </is>
       </c>
